--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104654_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104654_W22.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5377</v>
+        <v>4.6712</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2613</v>
+        <v>2.6117</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2764</v>
+        <v>2.0596</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4648</v>
+        <v>5.1858</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4417</v>
+        <v>1.8551</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0231</v>
+        <v>3.3307</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3047</v>
+        <v>3.6759</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1079</v>
+        <v>0.9653</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4126</v>
+        <v>2.7106</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1601</v>
+        <v>1.5099</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5496</v>
+        <v>0.8898</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0729</v>
+        <v>0.1895</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0907</v>
+        <v>-0.0838</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9822</v>
+        <v>0.2733</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8363</v>
+        <v>3.4828</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0221</v>
+        <v>0.2469</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8142</v>
+        <v>3.2359</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1817</v>
+        <v>2.4511</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8498</v>
+        <v>0.4314</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3319</v>
+        <v>2.0198</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6912</v>
+        <v>1.2715</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9697</v>
+        <v>-0.1281</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7214</v>
+        <v>1.3997</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4905</v>
+        <v>1.1796</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.5595</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6403</v>
+        <v>1.0317</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6956</v>
+        <v>0.1136</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0553</v>
+        <v>0.9181</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3529</v>
+        <v>3.0909</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9286</v>
+        <v>2.2413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4243</v>
+        <v>0.8495</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7736</v>
+        <v>1.8758</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9536</v>
+        <v>1.6254</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8201</v>
+        <v>0.2504</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0416</v>
+        <v>2.5621</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9871</v>
+        <v>2.0857</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0546</v>
+        <v>0.4764</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.268</v>
+        <v>-0.6863</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0335</v>
+        <v>-0.4603</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4963</v>
+        <v>-0.4482</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.113</v>
+        <v>-0.3207</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6093</v>
+        <v>-0.1275</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.7317</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7317</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9937</v>
+        <v>2.6593</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2475</v>
+        <v>2.7529</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2539</v>
+        <v>-0.0936</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1494</v>
+        <v>0.6861</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1169</v>
+        <v>2.2604</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9675</v>
+        <v>-1.5742</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6619</v>
+        <v>2.1749</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5499</v>
+        <v>2.7784</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>-0.6035</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5125</v>
+        <v>-1.4888</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.433</v>
+        <v>-0.518</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0795</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7782</v>
+        <v>-0.8792</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9467</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1685</v>
+        <v>-0.1983</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3856</v>
+        <v>4.6734</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>4.6734</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6538</v>
+        <v>2.6364</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0212</v>
+        <v>3.1422</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6326000000000001</v>
+        <v>-0.5059</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8697</v>
+        <v>3.7792</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6218</v>
+        <v>0.9671</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2479</v>
+        <v>2.812</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5777</v>
+        <v>4.0206</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0953</v>
+        <v>0.9825</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4824</v>
+        <v>3.0381</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.708</v>
+        <v>-0.2414</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4735</v>
+        <v>-0.0154</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8698</v>
+        <v>-0.2402</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.8784</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3133</v>
+        <v>0.6382</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-2.7237</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6286</v>
+        <v>2.5077</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1614</v>
+        <v>1.5515</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5329</v>
+        <v>0.9563</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6805</v>
+        <v>0.2254</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2611</v>
+        <v>0.9881</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5806</v>
+        <v>-0.7627</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1984</v>
+        <v>0.5249</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7982</v>
+        <v>1.4339</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5998</v>
+        <v>-0.909</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5179</v>
+        <v>-0.2995</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5371</v>
+        <v>-0.4458</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9808</v>
+        <v>0.1463</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9294</v>
+        <v>0.0547</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3266</v>
+        <v>-0.0629</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6028</v>
+        <v>0.1176</v>
       </c>
       <c r="V7" t="n">
-        <v>4.6921</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>4.6921</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9853</v>
+        <v>2.2751</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0827</v>
+        <v>5.2839</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9026</v>
+        <v>-3.0087</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2276</v>
+        <v>1.1508</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9899</v>
+        <v>2.1113</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7623</v>
+        <v>-0.9605</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5465</v>
+        <v>3.6453</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4475</v>
+        <v>3.5336</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.901</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3189</v>
+        <v>-2.4945</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4576</v>
+        <v>-1.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>-1.0722</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4691</v>
+        <v>0.0545</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>0.0044</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0501</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6697</v>
+        <v>1.7391</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0086</v>
+        <v>-0.0129</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6783</v>
+        <v>1.752</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0317</v>
+        <v>1.0401</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7012</v>
+        <v>0.7063</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3306</v>
+        <v>0.3338</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1785</v>
+        <v>0.1779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8532</v>
+        <v>0.8622</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1281</v>
+        <v>0.3274</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3738</v>
+        <v>-2.3838</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5019</v>
+        <v>2.7112</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1578</v>
+        <v>-0.165</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4544</v>
+        <v>2.4556</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6123</v>
+        <v>-2.6206</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4911</v>
+        <v>-1.517</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.2228</v>
+        <v>-3.2407</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3333</v>
+        <v>1.352</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1252</v>
+        <v>0.3346</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0907</v>
+        <v>0.1136</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0345</v>
+        <v>0.2211</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1306</v>
+        <v>-0.4998</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1026</v>
+        <v>-1.9022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.972</v>
+        <v>1.4024</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8501</v>
+        <v>-0.8495</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1544</v>
+        <v>-0.1523</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6957</v>
+        <v>-0.6972</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9762</v>
+        <v>-0.9962</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6722</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M11" t="n">
-        <v>0.126</v>
+        <v>0.1467</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3317</v>
+        <v>-0.6911</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0434</v>
+        <v>-0.8087</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2882</v>
+        <v>0.1176</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8682</v>
+        <v>-2.5116</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1767</v>
+        <v>-2.8674</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3086</v>
+        <v>0.3558</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8987</v>
+        <v>1.3092</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3478</v>
+        <v>0.8842</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.551</v>
+        <v>0.4249</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4116</v>
+        <v>0.5729</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7242</v>
+        <v>-0.1346</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6874</v>
+        <v>0.7075</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4871</v>
+        <v>0.7363</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3764</v>
+        <v>1.0189</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8636</v>
+        <v>-0.2826</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.65</v>
+        <v>0.0199</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.0258</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1152</v>
+        <v>0.0457</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8932</v>
+        <v>-2.7866</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8702</v>
+        <v>-3.0816</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.023</v>
+        <v>0.295</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2931</v>
+        <v>-2.904</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8772</v>
+        <v>-0.3475</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4159</v>
+        <v>-2.5564</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5807</v>
+        <v>-2.4333</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1283</v>
+        <v>-0.7347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.709</v>
+        <v>-1.6987</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7124</v>
+        <v>-0.4706</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0055</v>
+        <v>0.3871</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2931</v>
+        <v>-0.8578</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3451</v>
+        <v>-0.5655</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0484</v>
+        <v>-0.6483</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2967</v>
+        <v>0.0827</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.8941</v>
+        <v>17.5919</v>
       </c>
       <c r="E14" t="n">
-        <v>7.192900000000002</v>
+        <v>7.582499999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>9.7011</v>
+        <v>10.0095</v>
       </c>
       <c r="G14" t="n">
-        <v>13.7655</v>
+        <v>13.785</v>
       </c>
       <c r="H14" t="n">
-        <v>13.7654</v>
+        <v>13.7851</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001000000000000445</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="J14" t="n">
-        <v>13.9023</v>
+        <v>13.6795</v>
       </c>
       <c r="K14" t="n">
-        <v>12.0507</v>
+        <v>11.9261</v>
       </c>
       <c r="L14" t="n">
-        <v>1.851700000000001</v>
+        <v>1.7534</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1369000000000004</v>
+        <v>0.1056000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>1.7147</v>
+        <v>1.8588</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8517</v>
+        <v>-1.7535</v>
       </c>
       <c r="P14" t="n">
-        <v>2.268300000000001</v>
+        <v>2.276299999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7443</v>
+        <v>14.7963</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.192899999999999</v>
+        <v>-1.5085</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.3249</v>
+        <v>-3.626399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1321</v>
+        <v>2.1179</v>
       </c>
       <c r="V14" t="n">
-        <v>3.052999999999999</v>
+        <v>3.039199999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>10.0912</v>
+        <v>10.0494</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.0382</v>
+        <v>-7.0102</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2891</v>
+        <v>3.6379</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4073</v>
+        <v>2.8549</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8818</v>
+        <v>0.783</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6406</v>
+        <v>1.6391</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6118</v>
+        <v>0.6145</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0289</v>
+        <v>1.0247</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6045</v>
+        <v>2.5848</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7144</v>
+        <v>1.7064</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9639</v>
+        <v>-0.9457</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2589</v>
+        <v>0.0882</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6454</v>
+        <v>0.5206</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5147</v>
+        <v>3.0077</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9042</v>
+        <v>1.9734</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3895</v>
+        <v>1.0343</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5584</v>
+        <v>1.9719</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2612</v>
+        <v>1.9193</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8196</v>
+        <v>0.0526</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5636</v>
+        <v>2.3687</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6478</v>
+        <v>1.6612</v>
       </c>
       <c r="L16" t="n">
-        <v>4.2114</v>
+        <v>0.7075</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0052</v>
+        <v>-0.3968</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6134</v>
+        <v>0.2581</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>-0.6549</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3439</v>
+        <v>-0.1024</v>
       </c>
       <c r="T16" t="n">
-        <v>0.248</v>
+        <v>-0.3953</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0959</v>
+        <v>0.2929</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4186</v>
+        <v>2.6114</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0065</v>
+        <v>4.8807</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5878</v>
+        <v>-2.2693</v>
       </c>
       <c r="G17" t="n">
-        <v>1.511</v>
+        <v>0.5567</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4241</v>
+        <v>-3.2517</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9352</v>
+        <v>3.8085</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8762</v>
+        <v>3.5407</v>
       </c>
       <c r="K17" t="n">
-        <v>2.237</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6392</v>
+        <v>4.1924</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3652</v>
+        <v>-2.9839</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6611</v>
+        <v>-2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2959</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1079</v>
+        <v>0.44</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5989</v>
+        <v>0.2505</v>
       </c>
       <c r="U17" t="n">
-        <v>0.509</v>
+        <v>0.1895</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1604</v>
+        <v>1.7227</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5239</v>
+        <v>3.3704</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6366000000000001</v>
+        <v>-1.6478</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9765</v>
+        <v>1.5045</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9338</v>
+        <v>-0.4305</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0427</v>
+        <v>1.935</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3918</v>
+        <v>3.8436</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6828</v>
+        <v>2.2128</v>
       </c>
       <c r="L18" t="n">
-        <v>0.709</v>
+        <v>1.6308</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4153</v>
+        <v>-2.339</v>
       </c>
       <c r="N18" t="n">
-        <v>0.251</v>
+        <v>-2.6433</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6663</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9503</v>
+        <v>0.4261</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.868</v>
+        <v>0.0112</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0823</v>
+        <v>0.4149</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4469</v>
+        <v>-0.6508</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.87</v>
+        <v>-2.0162</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4231</v>
+        <v>1.3654</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4474</v>
+        <v>-0.4426</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4919</v>
+        <v>-2.4956</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0445</v>
+        <v>2.0531</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3099</v>
+        <v>-0.3315</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1757</v>
+        <v>-2.1933</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1375</v>
+        <v>-0.1111</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2519</v>
+        <v>0.0406</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5867</v>
+        <v>-0.7043</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8387</v>
+        <v>0.7449</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2168</v>
+        <v>-1.6817</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3905</v>
+        <v>-1.2569</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8263</v>
+        <v>-0.4247</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3704</v>
+        <v>-3.3847</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.8395</v>
+        <v>-3.8508</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4691</v>
+        <v>0.4661</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4065</v>
+        <v>-2.4391</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.7369</v>
+        <v>-2.7589</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9639</v>
+        <v>-0.9457</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.2949</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9648</v>
+        <v>0.1414</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2214</v>
+        <v>0.1535</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9267</v>
+        <v>-3.358</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8011</v>
+        <v>-2.5247</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1257</v>
+        <v>-0.8334</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.2429</v>
+        <v>-3.2893</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.8915</v>
+        <v>-0.9075</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3514</v>
+        <v>-2.3818</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.2094</v>
+        <v>-1.8715</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.3084</v>
+        <v>0.3857</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.901</v>
+        <v>-2.2572</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0335</v>
+        <v>-1.4179</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5831</v>
+        <v>-1.2932</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4504</v>
+        <v>-0.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4088</v>
+        <v>-0.1173</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3157</v>
+        <v>-0.6532</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0931</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4996</v>
+        <v>-3.6148</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8528</v>
+        <v>-2.8899</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.7249</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2891</v>
+        <v>-5.2521</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9062</v>
+        <v>-3.9026</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.383</v>
+        <v>-1.3495</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8457</v>
+        <v>-4.2367</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4014</v>
+        <v>-3.3277</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2471</v>
+        <v>-0.909</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4434</v>
+        <v>-1.0154</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3075</v>
+        <v>-0.5749</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1359</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2519</v>
+        <v>0.7268</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0071</v>
+        <v>0.2574</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7552</v>
+        <v>0.4694</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9313</v>
+        <v>-4.0738</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0227</v>
+        <v>-2.04</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9086</v>
+        <v>-2.0338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4628</v>
+        <v>0.4719</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6248</v>
+        <v>-0.6233</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0876</v>
+        <v>1.0952</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7658</v>
+        <v>0.7569</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0862</v>
+        <v>-0.0708</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5202</v>
+        <v>-0.5206</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.4498</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4701</v>
+        <v>-6.9495</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4542</v>
+        <v>-5.8896</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0159</v>
+        <v>-1.0599</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.776</v>
+        <v>-4.7753</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8789</v>
+        <v>-0.8707</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.8971</v>
+        <v>-3.9046</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.6525</v>
+        <v>-2.6676</v>
       </c>
       <c r="K24" t="n">
-        <v>0.381</v>
+        <v>0.3792</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.0335</v>
+        <v>-3.0469</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1234</v>
+        <v>-2.1077</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4258</v>
+        <v>0.1021</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>0.1925</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0266</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7856</v>
+        <v>-7.5459</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.1515</v>
+        <v>-6.4717</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6341</v>
+        <v>-1.0742</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.7891</v>
+        <v>-2.7851</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0071</v>
+        <v>0.014</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7962</v>
+        <v>-2.7991</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.641</v>
+        <v>-1.6539</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.148</v>
+        <v>-1.1312</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1376</v>
+        <v>0.3774</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9739</v>
+        <v>-0.2652</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1115</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.8942</v>
+        <v>-16.8948</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.700900000000001</v>
+        <v>-10.0096</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.1931</v>
+        <v>-6.885299999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-13.7656</v>
+        <v>-13.785</v>
       </c>
       <c r="H26" t="n">
-        <v>-13.7654</v>
+        <v>-13.7849</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>0.0002000000000008662</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1369000000000007</v>
+        <v>-0.1056000000000006</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.714699999999999</v>
+        <v>-1.8591</v>
       </c>
       <c r="L26" t="n">
-        <v>1.8517</v>
+        <v>1.7533</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.9023</v>
+        <v>-13.6795</v>
       </c>
       <c r="N26" t="n">
-        <v>-12.0507</v>
+        <v>-11.926</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8518</v>
+        <v>-1.7534</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2682</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q26" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1928</v>
+        <v>2.2056</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.132</v>
+        <v>-2.118</v>
       </c>
       <c r="U26" t="n">
-        <v>4.3249</v>
+        <v>4.3235</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.0531</v>
+        <v>-3.039200000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>7.0382</v>
+        <v>7.010199999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-10.0913</v>
+        <v>-10.0494</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104654_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104654_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.0102</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104654_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-10.0494</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
